--- a/Excel/MapModeConfig.xlsx
+++ b/Excel/MapModeConfig.xlsx
@@ -1221,6 +1221,38 @@
         <v>10</v>
       </c>
     </row>
+    <row r="7" customHeight="1" spans="3:14">
+      <c r="C7" s="1">
+        <v>2</v>
+      </c>
+      <c r="D7" s="1">
+        <v>73</v>
+      </c>
+      <c r="E7" s="1">
+        <v>144</v>
+      </c>
+      <c r="F7" s="1">
+        <v>2.3</v>
+      </c>
+      <c r="G7" s="1">
+        <v>2</v>
+      </c>
+      <c r="H7" s="1">
+        <v>1.6</v>
+      </c>
+      <c r="I7" s="1">
+        <v>4</v>
+      </c>
+      <c r="J7" s="1">
+        <v>5</v>
+      </c>
+      <c r="K7" s="1">
+        <v>10</v>
+      </c>
+      <c r="L7" s="1">
+        <v>10</v>
+      </c>
+    </row>
     <row r="30" customHeight="1" spans="1:2">
       <c r="A30" s="1" t="s">
         <v>13</v>
@@ -1234,7 +1266,7 @@
     <cfRule type="duplicateValues" dxfId="0" priority="9"/>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:C1048576" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:C5 C6:C7 C8:C1048576" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
